--- a/SGC-CKN/Excel/809c9292-332b-4724-8bfb-79289fd5b638_Lô_đất_ký_hiệu_CT-02_P11-122_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/809c9292-332b-4724-8bfb-79289fd5b638_Lô_đất_ký_hiệu_CT-02_P11-122_D800_19-03-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>14:10 19/03/2026</t>
+    <t>14:01 19/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -181,14 +181,14 @@
     <t>Cuội sạn sỏi</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">14:10
 19/03/2026</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -225,7 +225,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -301,12 +301,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF134E4A"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -324,7 +318,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -399,11 +393,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -608,22 +597,19 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1486,7 +1472,7 @@
         <v>50</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F19" s="31">
         <v>-44.6</v>
@@ -1495,67 +1481,67 @@
         <v>-45.5</v>
       </c>
       <c r="H19" s="31">
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="I19" s="31">
         <v>0.9</v>
       </c>
-      <c r="J19" s="34">
-        <v>0.54</v>
+      <c r="J19" s="8">
+        <v>1.8</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
+      <c r="D20" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="35">
+      <c r="F20" s="34">
         <v>-45.5</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <v>-50.07</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <v>1.67</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <v>4.57</v>
       </c>
       <c r="J20" s="8">
         <v>2.74</v>
       </c>
-      <c r="K20" s="36" t="s">
+      <c r="K20" s="35" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1929,38 +1915,38 @@
         <v>-45.5</v>
       </c>
       <c r="G10" s="31">
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="H10" s="31">
         <v>0.9</v>
       </c>
-      <c r="I10" s="34">
-        <v>0.54</v>
+      <c r="I10" s="8">
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="35">
+      <c r="B11" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <v>-45.5</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>-50.07</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <v>1.67</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>4.57</v>
       </c>
       <c r="I11" s="8">
@@ -1968,32 +1954,32 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>0</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="39">
         <v>-50.07</v>
       </c>
-      <c r="G12" s="40">
-        <v>8.83</v>
-      </c>
-      <c r="H12" s="40">
+      <c r="G12" s="39">
+        <v>7.67</v>
+      </c>
+      <c r="H12" s="39">
         <v>50.07</v>
       </c>
-      <c r="I12" s="40">
-        <v>5.67</v>
+      <c r="I12" s="39">
+        <v>6.53</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/809c9292-332b-4724-8bfb-79289fd5b638_Lô_đất_ký_hiệu_CT-02_P11-122_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/809c9292-332b-4724-8bfb-79289fd5b638_Lô_đất_ký_hiệu_CT-02_P11-122_D800_19-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
   <si>
     <t>Dự án</t>
   </si>
@@ -135,10 +135,10 @@
 19/03/2026</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">10:20
@@ -165,10 +165,10 @@
 19/03/2026</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ lẫn hạt cát nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">12:30
@@ -178,17 +178,23 @@
     <t>15</t>
   </si>
   <si>
-    <t>Cuội sạn sỏi</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+  </si>
+  <si>
+    <t>CS chạm sỏi</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:10
 19/03/2026</t>
+  </si>
+  <si>
+    <t>KT khoan</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1490,24 +1496,24 @@
         <v>1.8</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" s="34">
         <v>-45.5</v>
@@ -1525,12 +1531,12 @@
         <v>2.74</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1636,31 +1642,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1932,7 +1938,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1955,7 +1961,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>29</v>
